--- a/data/trans_orig/P36B09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2007</t>
+          <t>Población según la frecuencia de consumo de carne en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>31649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59043</t>
+          <t>58923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175720</t>
+          <t>175255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>218827</t>
+          <t>219968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107320</t>
+          <t>108934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>143927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>297325</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>352736</t>
+          <t>355130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176921</t>
+          <t>176525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218324</t>
+          <t>220707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127110</t>
+          <t>125253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162202</t>
+          <t>162393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315223</t>
+          <t>312957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>371554</t>
+          <t>370707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34007</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71667</t>
+          <t>72688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139039</t>
+          <t>139527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177706</t>
+          <t>179366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>158172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194776</t>
+          <t>195715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307995</t>
+          <t>307593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364082</t>
+          <t>364737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141804</t>
+          <t>141218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182462</t>
+          <t>180400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140279</t>
+          <t>138278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175354</t>
+          <t>177511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290801</t>
+          <t>291271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348943</t>
+          <t>347645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>54417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35824</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>201088</t>
+          <t>202665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>245947</t>
+          <t>249659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60645</t>
+          <t>61433</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>87035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274053</t>
+          <t>272729</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>325804</t>
+          <t>324038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214928</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>262929</t>
+          <t>265393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66879</t>
+          <t>65182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90758</t>
+          <t>90976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290087</t>
+          <t>288256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>343880</t>
+          <t>342157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>39446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77801</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>56957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49556</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65093</t>
+          <t>64165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100592</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457767</t>
+          <t>457698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>527169</t>
+          <t>526507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>280693</t>
+          <t>278026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>332076</t>
+          <t>330411</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>752218</t>
+          <t>750436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>840650</t>
+          <t>836696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>566021</t>
+          <t>564406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>635832</t>
+          <t>636753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>310645</t>
+          <t>309327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>361654</t>
+          <t>363955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>887809</t>
+          <t>895153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>977850</t>
+          <t>984051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75615</t>
+          <t>75766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113177</t>
+          <t>112678</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96077</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139912</t>
+          <t>138112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41183</t>
+          <t>40437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62943</t>
+          <t>63592</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102487</t>
+          <t>102029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>137869</t>
+          <t>136999</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>226545</t>
+          <t>227979</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>273600</t>
+          <t>275064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>340874</t>
+          <t>340962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>402719</t>
+          <t>402669</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>156675</t>
+          <t>158254</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>194452</t>
+          <t>197273</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>241256</t>
+          <t>237295</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>288098</t>
+          <t>288548</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>408724</t>
+          <t>406721</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>468469</t>
+          <t>470193</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>42265</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>42486</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72042</t>
+          <t>72485</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,47 +4192,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>17025</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>27321</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>17025</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>9602</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>26382</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,82 +4270,82 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>70312</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>55516</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>87794</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>77993</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>60914</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>97228</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>70312</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>54703</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>87706</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>77993</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>61313</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>96315</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>102697</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>134817</t>
+          <t>136285</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>568382</t>
+          <t>571065</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>637734</t>
+          <t>639575</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>684323</t>
+          <t>686328</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>760381</t>
+          <t>766891</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>129094</t>
+          <t>127864</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>161966</t>
+          <t>161234</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>489082</t>
+          <t>487824</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>559900</t>
+          <t>556545</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>628548</t>
+          <t>622299</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>706619</t>
+          <t>699762</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>53890</t>
+          <t>52513</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>81660</t>
+          <t>81549</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41536</t>
+          <t>43087</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>56796</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>92915</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>115191</t>
+          <t>116895</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>158854</t>
+          <t>162053</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>148513</t>
+          <t>147387</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>197848</t>
+          <t>199430</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>277297</t>
+          <t>278802</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>343192</t>
+          <t>346465</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1259501</t>
+          <t>1253941</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1373311</t>
+          <t>1369758</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1474175</t>
+          <t>1482223</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1591970</t>
+          <t>1594037</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2776249</t>
+          <t>2777636</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2941230</t>
+          <t>2939427</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1457790</t>
+          <t>1460494</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1576744</t>
+          <t>1573857</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1442779</t>
+          <t>1444330</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1553238</t>
+          <t>1557182</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2934426</t>
+          <t>2932577</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3095400</t>
+          <t>3100937</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>240717</t>
+          <t>237369</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>300993</t>
+          <t>300377</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>101773</t>
+          <t>102511</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>146806</t>
+          <t>146486</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>354917</t>
+          <t>353293</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>430992</t>
+          <t>431700</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2012</t>
+          <t>Población según la frecuencia de consumo de carne en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41440</t>
+          <t>40574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43387</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73277</t>
+          <t>75241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133849</t>
+          <t>134597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177913</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108874</t>
+          <t>108391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147667</t>
+          <t>145767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253138</t>
+          <t>254377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310460</t>
+          <t>307656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184116</t>
+          <t>185020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230773</t>
+          <t>228896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115772</t>
+          <t>114391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152814</t>
+          <t>150633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>312352</t>
+          <t>311415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>371623</t>
+          <t>370542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33773</t>
+          <t>33484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60445</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>83970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41193</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29998</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>62933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121216</t>
+          <t>122053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163344</t>
+          <t>163552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125341</t>
+          <t>124740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161979</t>
+          <t>163458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257817</t>
+          <t>257583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>315568</t>
+          <t>313717</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186849</t>
+          <t>185157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228070</t>
+          <t>228898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129808</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168373</t>
+          <t>168110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329736</t>
+          <t>329767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387185</t>
+          <t>386645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46754</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>75104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>46405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77958</t>
+          <t>77910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>33589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64788</t>
+          <t>65169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102586</t>
+          <t>103836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>211371</t>
+          <t>206731</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>261145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,47 +7345,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>124708</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>108873</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>140194</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>48,13%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>42,02%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>124708</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>108020</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139887</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>41,69%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>325808</t>
+          <t>327284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391226</t>
+          <t>389560</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>259777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>310732</t>
+          <t>314214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78542</t>
+          <t>80176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>111750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>351168</t>
+          <t>351878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>412711</t>
+          <t>410748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>32770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>49944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81551</t>
+          <t>81687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>30788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>62616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97660</t>
+          <t>96533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114674</t>
+          <t>114051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>162550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466310</t>
+          <t>466071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>535493</t>
+          <t>534082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289281</t>
+          <t>285220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>345109</t>
+          <t>343415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>762652</t>
+          <t>770917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>858917</t>
+          <t>863494</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>445793</t>
+          <t>447827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>516981</t>
+          <t>519962</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>284891</t>
+          <t>284933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>344903</t>
+          <t>340515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>749590</t>
+          <t>750695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>841568</t>
+          <t>837615</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57550</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91183</t>
+          <t>93879</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79084</t>
+          <t>79678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116529</t>
+          <t>116388</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161210</t>
+          <t>161335</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46537</t>
+          <t>45764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85606</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124208</t>
+          <t>124624</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115530</t>
+          <t>114376</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>162409</t>
+          <t>162438</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179137</t>
+          <t>181533</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>225130</t>
+          <t>224839</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>271590</t>
+          <t>271471</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>331131</t>
+          <t>327188</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>466187</t>
+          <t>466837</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>538190</t>
+          <t>536555</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>201136</t>
+          <t>200733</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>246005</t>
+          <t>246017</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>267056</t>
+          <t>269810</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>322590</t>
+          <t>326465</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>483728</t>
+          <t>483812</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>555493</t>
+          <t>554197</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>62084</t>
+          <t>61590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69584</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>79426</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>117678</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>76241</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>112900</t>
+          <t>110501</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>85517</t>
+          <t>84706</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>124811</t>
+          <t>123473</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>81903</t>
+          <t>80501</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111939</t>
+          <t>111646</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>505167</t>
+          <t>506384</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>573925</t>
+          <t>578195</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>600332</t>
+          <t>600038</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>677530</t>
+          <t>673047</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>115528</t>
+          <t>115191</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>147026</t>
+          <t>147735</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>384356</t>
+          <t>385662</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>449582</t>
+          <t>451055</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>510929</t>
+          <t>513846</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>584444</t>
+          <t>586350</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35840</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>29795</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>51217</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>83074</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>45107</t>
+          <t>42716</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>61445</t>
+          <t>62710</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>58301</t>
+          <t>61067</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>95417</t>
+          <t>100088</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>207480</t>
+          <t>205951</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>270548</t>
+          <t>268641</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>290508</t>
+          <t>287063</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>361273</t>
+          <t>358997</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>515171</t>
+          <t>515938</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>607920</t>
+          <t>611760</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1275457</t>
+          <t>1274328</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1392585</t>
+          <t>1392002</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1484350</t>
+          <t>1485054</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1612382</t>
+          <t>1611381</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2790043</t>
+          <t>2785595</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2956878</t>
+          <t>2950900</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1474487</t>
+          <t>1478172</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1596081</t>
+          <t>1593684</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1344053</t>
+          <t>1343955</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1464475</t>
+          <t>1468466</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2856912</t>
+          <t>2863048</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3029925</t>
+          <t>3023585</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>241214</t>
+          <t>243396</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>306362</t>
+          <t>308236</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>187683</t>
+          <t>189059</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>246158</t>
+          <t>246851</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>444414</t>
+          <t>444172</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>531473</t>
+          <t>531061</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2016</t>
+          <t>Población según la frecuencia de consumo de carne en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>67405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159572</t>
+          <t>155796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199978</t>
+          <t>199628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116303</t>
+          <t>118161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>153065</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>287482</t>
+          <t>286864</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344942</t>
+          <t>344561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145154</t>
+          <t>147150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>188071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122632</t>
+          <t>121832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160664</t>
+          <t>159494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279516</t>
+          <t>279062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337122</t>
+          <t>335052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34775</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61474</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69678</t>
+          <t>66214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103072</t>
+          <t>102548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47345</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106626</t>
+          <t>108152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144241</t>
+          <t>145793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135492</t>
+          <t>132812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>172481</t>
+          <t>172507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>249568</t>
+          <t>252826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>304673</t>
+          <t>307561</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163865</t>
+          <t>162127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202160</t>
+          <t>200999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129834</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166136</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>307055</t>
+          <t>305409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362063</t>
+          <t>360336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37271</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>55914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74186</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111682</t>
+          <t>112050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>31018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158963</t>
+          <t>162706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203474</t>
+          <t>205916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>53945</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>79432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>222923</t>
+          <t>226836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273484</t>
+          <t>278215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217238</t>
+          <t>217593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>263036</t>
+          <t>263910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>286911</t>
+          <t>285647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>340023</t>
+          <t>339104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61469</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94008</t>
+          <t>94627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30962</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>77856</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115317</t>
+          <t>115215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38503</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62255</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>353419</t>
+          <t>356095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>417593</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>283584</t>
+          <t>282990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338923</t>
+          <t>340448</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>653154</t>
+          <t>654834</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>740026</t>
+          <t>738833</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>519034</t>
+          <t>521378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>591337</t>
+          <t>592610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>332945</t>
+          <t>333930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>389920</t>
+          <t>389965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>871910</t>
+          <t>876293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>963004</t>
+          <t>959758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148570</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197014</t>
+          <t>200799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100249</t>
+          <t>101466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139432</t>
+          <t>140027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>262257</t>
+          <t>264361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326955</t>
+          <t>325272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36387</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>32491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59227</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>177474</t>
+          <t>176242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>224403</t>
+          <t>222430</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>268076</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>322483</t>
+          <t>325698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>461245</t>
+          <t>460366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>531896</t>
+          <t>534856</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>262332</t>
+          <t>266088</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>315571</t>
+          <t>317916</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>252218</t>
+          <t>255379</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>307934</t>
+          <t>307181</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>538577</t>
+          <t>537073</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>616274</t>
+          <t>608090</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126676</t>
+          <t>127230</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>107014</t>
+          <t>104844</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>148759</t>
+          <t>149548</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>204372</t>
+          <t>205452</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>261507</t>
+          <t>262258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>67724</t>
+          <t>69066</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>69898</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>98748</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>409408</t>
+          <t>408221</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>477371</t>
+          <t>475235</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>489155</t>
+          <t>491201</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>564040</t>
+          <t>563622</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>142902</t>
+          <t>143571</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>176548</t>
+          <t>175556</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>394861</t>
+          <t>388545</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>460936</t>
+          <t>456401</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>546184</t>
+          <t>546674</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>622170</t>
+          <t>619711</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>28885</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>129009</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>175622</t>
+          <t>176765</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>166848</t>
+          <t>166653</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>219681</t>
+          <t>221929</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47845</t>
+          <t>48178</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>79860</t>
+          <t>80311</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>81973</t>
+          <t>81169</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>125815</t>
+          <t>125000</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>178328</t>
+          <t>174264</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>221320</t>
+          <t>212454</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>283557</t>
+          <t>277636</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1097136</t>
+          <t>1101089</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1213606</t>
+          <t>1215444</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1341976</t>
+          <t>1343289</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1466733</t>
+          <t>1462856</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2476902</t>
+          <t>2482024</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2646525</t>
+          <t>2642883</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1539447</t>
+          <t>1539342</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1659711</t>
+          <t>1657475</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1376693</t>
+          <t>1371860</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1496592</t>
+          <t>1486522</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2949642</t>
+          <t>2950437</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3119493</t>
+          <t>3114843</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>453379</t>
+          <t>452299</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>535119</t>
+          <t>535793</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>458544</t>
+          <t>456836</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>537797</t>
+          <t>542094</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>933154</t>
+          <t>932996</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1049354</t>
+          <t>1046186</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58923</t>
+          <t>58967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175255</t>
+          <t>179926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>219968</t>
+          <t>221198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108934</t>
+          <t>109108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143927</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>297325</t>
+          <t>296831</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>355130</t>
+          <t>354086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176525</t>
+          <t>176358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220707</t>
+          <t>218792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125253</t>
+          <t>126284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162393</t>
+          <t>160067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>312957</t>
+          <t>312030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370707</t>
+          <t>369698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>60695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139527</t>
+          <t>138801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179366</t>
+          <t>179643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158172</t>
+          <t>157270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195715</t>
+          <t>195492</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307593</t>
+          <t>305660</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364737</t>
+          <t>360983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>140367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180400</t>
+          <t>180213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138278</t>
+          <t>138543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177511</t>
+          <t>176524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291271</t>
+          <t>291129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>347645</t>
+          <t>347353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26931</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54417</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>202665</t>
+          <t>202499</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249659</t>
+          <t>247400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61433</t>
+          <t>61029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87035</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>272729</t>
+          <t>271248</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324038</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216340</t>
+          <t>216804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>265393</t>
+          <t>262420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65182</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90976</t>
+          <t>89963</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>290191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>342157</t>
+          <t>343288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39446</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>45866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75971</t>
+          <t>77635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56957</t>
+          <t>57807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64165</t>
+          <t>63028</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99695</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457698</t>
+          <t>460224</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>526507</t>
+          <t>528519</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>278026</t>
+          <t>278656</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>330411</t>
+          <t>330142</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>750436</t>
+          <t>753164</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>836696</t>
+          <t>843649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>564114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>636753</t>
+          <t>637206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>309327</t>
+          <t>311441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>363955</t>
+          <t>363656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>895153</t>
+          <t>891775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>984051</t>
+          <t>983795</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>74476</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112678</t>
+          <t>110643</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138112</t>
+          <t>141909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40437</t>
+          <t>39149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>36058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63592</t>
+          <t>64799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102029</t>
+          <t>101313</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136999</t>
+          <t>136393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>227979</t>
+          <t>227186</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>275064</t>
+          <t>275839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>340962</t>
+          <t>343784</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>402669</t>
+          <t>401214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>158254</t>
+          <t>156412</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>197273</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>237295</t>
+          <t>238965</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>288548</t>
+          <t>286530</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>406721</t>
+          <t>403950</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>470193</t>
+          <t>468995</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>36352</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>41722</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72485</t>
+          <t>71192</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>27188</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>55516</t>
+          <t>56138</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>87849</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>97228</t>
+          <t>96496</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>102697</t>
+          <t>103216</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>135549</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>571065</t>
+          <t>570351</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>639575</t>
+          <t>642162</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>686328</t>
+          <t>686154</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>766891</t>
+          <t>762613</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>127864</t>
+          <t>129679</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>161234</t>
+          <t>162775</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>487824</t>
+          <t>483442</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>556545</t>
+          <t>554335</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>622299</t>
+          <t>627568</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>699762</t>
+          <t>704618</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>50214</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>81549</t>
+          <t>80962</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>57093</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>92915</t>
+          <t>91344</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>116895</t>
+          <t>117060</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>162053</t>
+          <t>161285</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>147387</t>
+          <t>148089</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>199430</t>
+          <t>200564</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>278802</t>
+          <t>274282</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>346465</t>
+          <t>340855</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1253941</t>
+          <t>1264462</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1369758</t>
+          <t>1372042</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1482223</t>
+          <t>1483095</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1594037</t>
+          <t>1600721</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2777636</t>
+          <t>2769330</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2939427</t>
+          <t>2933854</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1460494</t>
+          <t>1459494</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1573857</t>
+          <t>1572166</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1444330</t>
+          <t>1439545</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1557182</t>
+          <t>1552294</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2932577</t>
+          <t>2936502</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3100937</t>
+          <t>3096547</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>237369</t>
+          <t>238125</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>300377</t>
+          <t>300440</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>102511</t>
+          <t>102105</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>146486</t>
+          <t>146616</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>353293</t>
+          <t>357289</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>431700</t>
+          <t>435961</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40574</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41858</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75241</t>
+          <t>73613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134597</t>
+          <t>136913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>176488</t>
+          <t>177374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108391</t>
+          <t>109240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145767</t>
+          <t>145212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254377</t>
+          <t>255947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>307656</t>
+          <t>308565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>185020</t>
+          <t>184645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228896</t>
+          <t>227368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114391</t>
+          <t>113477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150633</t>
+          <t>150718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311415</t>
+          <t>314088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370542</t>
+          <t>372129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33484</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60221</t>
+          <t>59192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>51574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83970</t>
+          <t>81776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>41690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62933</t>
+          <t>62668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122053</t>
+          <t>122005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163552</t>
+          <t>161729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>124740</t>
+          <t>125505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163458</t>
+          <t>163376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257583</t>
+          <t>257184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>313717</t>
+          <t>312523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185157</t>
+          <t>185451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228898</t>
+          <t>229218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129891</t>
+          <t>130233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168110</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329767</t>
+          <t>331016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386645</t>
+          <t>388930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43968</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46405</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77910</t>
+          <t>76763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65169</t>
+          <t>64777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103836</t>
+          <t>102100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206731</t>
+          <t>210075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261145</t>
+          <t>260100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108873</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140194</t>
+          <t>140279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>327284</t>
+          <t>328833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>389560</t>
+          <t>390236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>259777</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>314214</t>
+          <t>310911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>79788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111750</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>351878</t>
+          <t>351725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>410748</t>
+          <t>412939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60044</t>
+          <t>61167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49944</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81687</t>
+          <t>81270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62616</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96533</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>76438</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114051</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162550</t>
+          <t>158962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466071</t>
+          <t>464360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>534082</t>
+          <t>536253</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>285220</t>
+          <t>284015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>339795</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>770917</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>863494</t>
+          <t>858043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>447827</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>519962</t>
+          <t>516394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>284933</t>
+          <t>287391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340515</t>
+          <t>344123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>750695</t>
+          <t>750851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>837615</t>
+          <t>841176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93879</t>
+          <t>93906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47885</t>
+          <t>47294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79678</t>
+          <t>79515</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116388</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161335</t>
+          <t>161045</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23779</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45764</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>86108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124624</t>
+          <t>125785</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114376</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>162438</t>
+          <t>161082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>181533</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>224839</t>
+          <t>225100</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>271471</t>
+          <t>270738</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>327188</t>
+          <t>328767</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>466837</t>
+          <t>465465</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>536555</t>
+          <t>536028</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>200733</t>
+          <t>199820</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>246017</t>
+          <t>246103</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>269810</t>
+          <t>268409</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>326465</t>
+          <t>323980</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>483812</t>
+          <t>481917</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>554197</t>
+          <t>550742</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>61938</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66049</t>
+          <t>65986</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>79426</t>
+          <t>81146</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>117678</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>72165</t>
+          <t>74147</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>110501</t>
+          <t>110908</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>123473</t>
+          <t>123123</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>81632</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111646</t>
+          <t>112421</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>506384</t>
+          <t>501481</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>578195</t>
+          <t>573717</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>600038</t>
+          <t>597286</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>673047</t>
+          <t>673199</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>115191</t>
+          <t>118310</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>147735</t>
+          <t>149424</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>385662</t>
+          <t>386387</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>451055</t>
+          <t>449061</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>513846</t>
+          <t>513996</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>586350</t>
+          <t>590775</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>36209</t>
+          <t>35504</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>51217</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>83002</t>
+          <t>80825</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>62710</t>
+          <t>61892</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>100088</t>
+          <t>97402</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>205951</t>
+          <t>206611</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>268641</t>
+          <t>272290</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>287063</t>
+          <t>287617</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>358997</t>
+          <t>363158</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>515938</t>
+          <t>517229</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>611760</t>
+          <t>614551</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1274328</t>
+          <t>1268691</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1392002</t>
+          <t>1389887</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1485054</t>
+          <t>1481064</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1611381</t>
+          <t>1604720</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2785595</t>
+          <t>2782305</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2950900</t>
+          <t>2960064</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1478172</t>
+          <t>1475161</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1593684</t>
+          <t>1601803</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1343955</t>
+          <t>1343279</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1468466</t>
+          <t>1465054</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2863048</t>
+          <t>2858866</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3023585</t>
+          <t>3033550</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>243396</t>
+          <t>242776</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>308236</t>
+          <t>304769</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>189059</t>
+          <t>189090</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>246851</t>
+          <t>250779</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>444172</t>
+          <t>442061</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>531061</t>
+          <t>526300</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43753</t>
+          <t>43378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>67795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155796</t>
+          <t>158892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199628</t>
+          <t>200344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118161</t>
+          <t>117109</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154568</t>
+          <t>155009</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>286864</t>
+          <t>286854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344561</t>
+          <t>343796</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147150</t>
+          <t>146515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188071</t>
+          <t>186732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121832</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159494</t>
+          <t>158897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279062</t>
+          <t>278394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335052</t>
+          <t>336568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34687</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>63139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52209</t>
+          <t>52805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66214</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102548</t>
+          <t>104113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23288</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108152</t>
+          <t>109594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145793</t>
+          <t>146967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132812</t>
+          <t>134155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>172507</t>
+          <t>172318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252826</t>
+          <t>255081</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307561</t>
+          <t>307380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162127</t>
+          <t>162369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200999</t>
+          <t>199929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128527</t>
+          <t>130566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>167347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305409</t>
+          <t>305008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360336</t>
+          <t>358290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66891</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55914</t>
+          <t>57001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>72904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112050</t>
+          <t>112142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162706</t>
+          <t>161718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>205916</t>
+          <t>204750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53945</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79432</t>
+          <t>79023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>226836</t>
+          <t>223523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>278215</t>
+          <t>273373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217593</t>
+          <t>217645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>263910</t>
+          <t>262753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60098</t>
+          <t>59023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86543</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285647</t>
+          <t>286584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339104</t>
+          <t>336854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94627</t>
+          <t>92251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77856</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115215</t>
+          <t>116364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>31439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>37007</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>34938</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>63880</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>356095</t>
+          <t>355725</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>422326</t>
+          <t>420624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282990</t>
+          <t>282857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>340448</t>
+          <t>339732</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>654834</t>
+          <t>654052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>738833</t>
+          <t>742516</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521378</t>
+          <t>524783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>592610</t>
+          <t>590254</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>333930</t>
+          <t>334937</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>389965</t>
+          <t>393462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>876293</t>
+          <t>873720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>959758</t>
+          <t>967666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148563</t>
+          <t>148741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>200799</t>
+          <t>197339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101466</t>
+          <t>99231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140027</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264361</t>
+          <t>261652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>325272</t>
+          <t>322813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29222</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37271</t>
+          <t>37451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32491</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>176242</t>
+          <t>176279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222430</t>
+          <t>222549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>268076</t>
+          <t>268611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>325698</t>
+          <t>324944</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>460366</t>
+          <t>462216</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>534856</t>
+          <t>532135</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>266088</t>
+          <t>267234</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>317916</t>
+          <t>316265</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>255379</t>
+          <t>255734</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>307181</t>
+          <t>309260</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>537073</t>
+          <t>536386</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608090</t>
+          <t>609882</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>89555</t>
+          <t>89026</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>127230</t>
+          <t>127700</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>104844</t>
+          <t>107191</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>149548</t>
+          <t>149243</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205452</t>
+          <t>206212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>262258</t>
+          <t>264363</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>65389</t>
+          <t>65749</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>67781</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69898</t>
+          <t>68163</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98748</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>408221</t>
+          <t>406965</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>475235</t>
+          <t>476622</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>491201</t>
+          <t>490858</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>563622</t>
+          <t>563057</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>143571</t>
+          <t>143952</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>175556</t>
+          <t>177607</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>388545</t>
+          <t>389726</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>456401</t>
+          <t>459142</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>546674</t>
+          <t>547223</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>619711</t>
+          <t>621196</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>52163</t>
+          <t>54685</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>129891</t>
+          <t>128959</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>176765</t>
+          <t>174384</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>165986</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>221929</t>
+          <t>218938</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>57187</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>48003</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>80215</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>81169</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>121807</t>
+          <t>121910</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>125000</t>
+          <t>126188</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>174264</t>
+          <t>176331</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>212454</t>
+          <t>218193</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>277636</t>
+          <t>283081</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1101089</t>
+          <t>1103023</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1215444</t>
+          <t>1217289</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1343289</t>
+          <t>1345104</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1462856</t>
+          <t>1468979</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2482024</t>
+          <t>2474390</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2642883</t>
+          <t>2642151</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1539342</t>
+          <t>1537063</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1657475</t>
+          <t>1654947</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1371860</t>
+          <t>1369409</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1486522</t>
+          <t>1489279</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2950437</t>
+          <t>2940922</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3114843</t>
+          <t>3115157</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>452299</t>
+          <t>452966</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>535793</t>
+          <t>535437</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>456836</t>
+          <t>456487</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>542094</t>
+          <t>542169</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>932996</t>
+          <t>933442</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1046186</t>
+          <t>1050716</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
